--- a/data/trans_dic/IP16B98-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero otros medicamentos recetados por el médico</t>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -636,27 +637,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>24,67; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,63; 100,0</t>
+          <t>35,81; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,71; 100,0</t>
+          <t>47,52; 100,0</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,12; 100,0</t>
+          <t>51,66; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,29; 100,0</t>
+          <t>47,1; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 100,0</t>
+          <t>43,89; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,73; 96,01</t>
+          <t>63,53; 96,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,03; 100,0</t>
+          <t>70,45; 100,0</t>
         </is>
       </c>
     </row>
@@ -951,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1111,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,08; 100,0</t>
+          <t>76,51; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,79; 100,0</t>
+          <t>87,7; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,97; 100,0</t>
+          <t>73,48; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,73; 100,0</t>
+          <t>78,39; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,54; 98,21</t>
+          <t>81,93; 98,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,39; 98,69</t>
+          <t>86,54; 98,71</t>
         </is>
       </c>
     </row>
@@ -1163,4 +1164,944 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2283</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3420</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1994</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>593; 2402</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1433; 4002</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2226; 4685</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2652</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3967</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7947</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5897</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13952</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14349</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3426; 6632</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4577; 9717</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3256; 7419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10388; 15708</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11181; 15871</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4226</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7615</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9997</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>14981</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20550</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20175</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>19573</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35155</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>40123</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>12387; 16190</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18508; 21104</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>16125; 21946</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>16536; 21095</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>31245; 37465</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>36518; 41655</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B98-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Clase-trans_dic.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,67; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,81; 100,0</t>
+          <t>36,47; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,52; 100,0</t>
+          <t>46,03; 100,0</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,66; 100,0</t>
+          <t>60,89; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,1; 100,0</t>
+          <t>46,69; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,89; 100,0</t>
+          <t>44,17; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,53; 96,07</t>
+          <t>62,66; 96,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,45; 100,0</t>
+          <t>70,92; 100,0</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>76,51; 100,0</t>
+          <t>76,89; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,7; 100,0</t>
+          <t>85,68; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,48; 100,0</t>
+          <t>75,73; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,39; 100,0</t>
+          <t>77,85; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,93; 98,24</t>
+          <t>81,93; 97,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,54; 98,71</t>
+          <t>87,25; 98,68</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>593; 2402</t>
+          <t>0; 2402</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1433; 4002</t>
+          <t>1460; 4002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2226; 4685</t>
+          <t>2157; 4685</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3426; 6632</t>
+          <t>4039; 6632</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4577; 9717</t>
+          <t>4537; 9717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3256; 7419</t>
+          <t>3277; 7419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10388; 15708</t>
+          <t>10244; 15717</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11181; 15871</t>
+          <t>11255; 15871</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12387; 16190</t>
+          <t>12448; 16190</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18508; 21104</t>
+          <t>18082; 21104</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16125; 21946</t>
+          <t>16619; 21946</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16536; 21095</t>
+          <t>16423; 21095</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31245; 37465</t>
+          <t>31243; 37044</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36518; 41655</t>
+          <t>36820; 41644</t>
         </is>
       </c>
     </row>
